--- a/sheets/민요/검수/천안 삼거리-굿거리.xlsx
+++ b/sheets/민요/검수/천안 삼거리-굿거리.xlsx
@@ -266,7 +266,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">sheets/민요/csv/천안 삼거리 (굿거리).csv</t>
+          <t xml:space="preserve">sheets/민요/csv/천안 삼거리-굿거리.csv</t>
         </is>
       </c>
     </row>

--- a/sheets/민요/검수/천안 삼거리-굿거리.xlsx
+++ b/sheets/민요/검수/천안 삼거리-굿거리.xlsx
@@ -65,10 +65,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="solid">

--- a/sheets/민요/검수/천안 삼거리-굿거리.xlsx
+++ b/sheets/민요/검수/천안 삼거리-굿거리.xlsx
@@ -3134,6 +3134,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -3150,10 +3153,10 @@
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="77.61" customHeight="1">
+    <row r="2" ht="60.61" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3172,7 +3175,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="77.61" customHeight="1">
+    <row r="3" ht="90.2" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3235,7 +3238,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="77.61" customHeight="1">
+    <row r="4" ht="90.2" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3298,7 +3301,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="77.61" customHeight="1">
+    <row r="5" ht="90.2" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3357,7 +3360,7 @@
       </c>
       <c r="M5" s="27"/>
     </row>
-    <row r="6" ht="77.61" customHeight="1">
+    <row r="6" ht="90.2" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3420,7 +3423,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="77.61" customHeight="1">
+    <row r="7" ht="90.2" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3475,7 +3478,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="77.61" customHeight="1">
+    <row r="8" ht="90.2" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="23" t="inlineStr">
         <is>
@@ -3541,7 +3544,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="77.61" customHeight="1">
+    <row r="9" ht="90.2" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3604,7 +3607,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="77.61" customHeight="1">
+    <row r="10" ht="90.2" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3635,7 +3638,7 @@
       </c>
       <c r="M10" s="25"/>
     </row>
-    <row r="11" ht="77.61" customHeight="1">
+    <row r="11" ht="90.2" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3680,7 +3683,7 @@
       </c>
       <c r="M11" s="26"/>
     </row>
-    <row r="12" ht="77.61" customHeight="1">
+    <row r="12" ht="90.2" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -3739,7 +3742,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="77.61" customHeight="1">
+    <row r="13" ht="90.2" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -3774,7 +3777,7 @@
       </c>
       <c r="M13" s="25"/>
     </row>
-    <row r="14" ht="77.61" customHeight="1">
+    <row r="14" ht="90.2" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3820,6 +3823,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/천안 삼거리-굿거리.xlsx
+++ b/sheets/민요/검수/천안 삼거리-굿거리.xlsx
@@ -3139,24 +3139,24 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60.61" customHeight="true">
+    <row r="2" ht="48.19" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="90.2" customHeight="true">
+    <row r="3" ht="71.62" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="90.2" customHeight="true">
+    <row r="4" ht="71.62" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="90.2" customHeight="true">
+    <row r="5" ht="71.62" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="M5" s="27"/>
     </row>
-    <row r="6" ht="90.2" customHeight="true">
+    <row r="6" ht="71.62" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="90.2" customHeight="true">
+    <row r="7" ht="71.62" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="90.2" customHeight="true">
+    <row r="8" ht="71.62" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="23" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="90.2" customHeight="true">
+    <row r="9" ht="71.62" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="90.2" customHeight="true">
+    <row r="10" ht="71.62" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
       </c>
       <c r="M10" s="25"/>
     </row>
-    <row r="11" ht="90.2" customHeight="true">
+    <row r="11" ht="71.62" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="M11" s="26"/>
     </row>
-    <row r="12" ht="90.2" customHeight="true">
+    <row r="12" ht="71.62" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="90.2" customHeight="true">
+    <row r="13" ht="71.62" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="M13" s="25"/>
     </row>
-    <row r="14" ht="90.2" customHeight="true">
+    <row r="14" ht="71.62" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3823,6 +3823,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="83"/>
 </worksheet>
 </file>